--- a/sheets/조재수대금교본/검수/여로.xlsx
+++ b/sheets/조재수대금교본/검수/여로.xlsx
@@ -2480,7 +2480,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -2496,7 +2496,6 @@
         <is>
           <t xml:space="preserve">仲
 –
-ﾉ
 太</t>
         </is>
       </c>
@@ -2535,11 +2534,7 @@
     </row>
     <row r="5" ht="144.45" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="23"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
@@ -2566,22 +2561,13 @@
       <c r="C6" s="24"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="E6" s="24"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="24"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="24"/>
     </row>
     <row r="7" ht="144.45" customHeight="true">
@@ -2595,7 +2581,7 @@
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-潢∧
+潢
 –</t>
         </is>
       </c>
@@ -2637,8 +2623,7 @@
         <is>
           <t xml:space="preserve">無
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G8" s="23"/>
@@ -2680,30 +2665,19 @@
         <is>
           <t xml:space="preserve">無
 南
-ﾉ
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="C10" s="24"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
     </row>
     <row r="11" ht="144.45" customHeight="true">
@@ -2764,11 +2738,7 @@
     </row>
     <row r="13" ht="144.45" customHeight="true">
       <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B13" s="21"/>
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
@@ -2795,23 +2765,17 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∼
-‹</t>
+          <t xml:space="preserve">汰∼</t>
         </is>
       </c>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
     </row>
     <row r="15" ht="144.45" customHeight="true">
@@ -2833,7 +2797,7 @@
       <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–ﾉ
+–
 太</t>
         </is>
       </c>
@@ -2841,7 +2805,7 @@
       <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–ﾉ
+–
 太</t>
         </is>
       </c>
@@ -2865,7 +2829,7 @@
       <c r="E16" s="23"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅂ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G16" s="23"/>
@@ -2911,8 +2875,7 @@
         <is>
           <t xml:space="preserve">㳞
 汰
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="E18" s="24"/>

--- a/sheets/조재수대금교본/검수/여로.xlsx
+++ b/sheets/조재수대금교본/검수/여로.xlsx
@@ -2480,7 +2480,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㅋ</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -2496,6 +2496,7 @@
         <is>
           <t xml:space="preserve">仲
 –
+ﾉ
 太</t>
         </is>
       </c>
@@ -2581,7 +2582,7 @@
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-潢
+潢∧
 –</t>
         </is>
       </c>
@@ -2665,6 +2666,7 @@
         <is>
           <t xml:space="preserve">無
 南
+ﾉ
 –</t>
         </is>
       </c>
@@ -2797,7 +2799,7 @@
       <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–
+–ﾉ
 太</t>
         </is>
       </c>
@@ -2805,7 +2807,7 @@
       <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–
+–ﾉ
 太</t>
         </is>
       </c>
@@ -2829,7 +2831,7 @@
       <c r="E16" s="23"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㅂ</t>
         </is>
       </c>
       <c r="G16" s="23"/>

--- a/sheets/조재수대금교본/검수/여로.xlsx
+++ b/sheets/조재수대금교본/검수/여로.xlsx
@@ -2448,20 +2448,20 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="129.03" customHeight="true">
+    <row r="2" ht="105.26" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="144.45" customHeight="true">
+    <row r="3" ht="117.77" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="144.45" customHeight="true">
+    <row r="4" ht="117.77" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="144.45" customHeight="true">
+    <row r="5" ht="117.77" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -2550,7 +2550,7 @@
       <c r="H5" s="21"/>
       <c r="I5" s="23"/>
     </row>
-    <row r="6" ht="144.45" customHeight="true">
+    <row r="6" ht="117.77" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
       <c r="H6" s="21"/>
       <c r="I6" s="24"/>
     </row>
-    <row r="7" ht="144.45" customHeight="true">
+    <row r="7" ht="117.77" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" ht="144.45" customHeight="true">
+    <row r="8" ht="117.77" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="I8" s="23"/>
     </row>
-    <row r="9" ht="144.45" customHeight="true">
+    <row r="9" ht="117.77" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
       <c r="H9" s="21"/>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" ht="144.45" customHeight="true">
+    <row r="10" ht="117.77" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
       <c r="H10" s="21"/>
       <c r="I10" s="24"/>
     </row>
-    <row r="11" ht="144.45" customHeight="true">
+    <row r="11" ht="117.77" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="I11" s="22"/>
     </row>
-    <row r="12" ht="144.45" customHeight="true">
+    <row r="12" ht="117.77" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="I12" s="23"/>
     </row>
-    <row r="13" ht="144.45" customHeight="true">
+    <row r="13" ht="117.77" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2755,7 +2755,7 @@
       <c r="H13" s="21"/>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="144.45" customHeight="true">
+    <row r="14" ht="117.77" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       <c r="H14" s="21"/>
       <c r="I14" s="24"/>
     </row>
-    <row r="15" ht="144.45" customHeight="true">
+    <row r="15" ht="117.77" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I15" s="22"/>
     </row>
-    <row r="16" ht="144.45" customHeight="true">
+    <row r="16" ht="117.77" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="I16" s="23"/>
     </row>
-    <row r="17" ht="144.45" customHeight="true">
+    <row r="17" ht="117.77" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
       <c r="H17" s="21"/>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" ht="144.45" customHeight="true">
+    <row r="18" ht="117.77" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -2892,6 +2892,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="31"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="38"/>
 </worksheet>
 </file>